--- a/data/gravel/Breezer Thunder 2025.xlsx
+++ b/data/gravel/Breezer Thunder 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD04710-0F9E-224F-A536-6FCDF2349CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B36644A-E747-5848-92F9-730B3A648EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38700" yWindow="-22060" windowWidth="28560" windowHeight="18300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8560" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="105">
   <si>
     <t>brand</t>
   </si>
@@ -345,6 +345,9 @@
   </si>
   <si>
     <t>a8:f31</t>
+  </si>
+  <si>
+    <t>https://www.breezerbikes.com/cdn/shop/files/2021_BREEZER_THUNDER_GRAY_BURNTORANGE.jpg?v=1740772941&amp;width=5000</t>
   </si>
 </sst>
 </file>
@@ -730,6 +733,11 @@
         <v>95</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>104</v>
+      </c>
+    </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>

--- a/data/gravel/Breezer Thunder 2025.xlsx
+++ b/data/gravel/Breezer Thunder 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B36644A-E747-5848-92F9-730B3A648EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F68BF63F-7C22-534C-9D7D-0A713B8499DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8560" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -348,6 +348,12 @@
   </si>
   <si>
     <t>https://www.breezerbikes.com/cdn/shop/files/2021_BREEZER_THUNDER_GRAY_BURNTORANGE.jpg?v=1740772941&amp;width=5000</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania, USA</t>
   </si>
 </sst>
 </file>
@@ -687,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N71"/>
+  <dimension ref="A1:N72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1450,6 +1456,14 @@
         <v>90</v>
       </c>
     </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>105</v>
+      </c>
+      <c r="B72" t="s">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Breezer Thunder 2025.xlsx
+++ b/data/gravel/Breezer Thunder 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F68BF63F-7C22-534C-9D7D-0A713B8499DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB329038-DE67-274E-A348-D4D42A1CB3FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="113">
   <si>
     <t>brand</t>
   </si>
@@ -354,6 +354,24 @@
   </si>
   <si>
     <t>Philadelphia, Pennsylvania, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -693,7 +711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N72"/>
+  <dimension ref="A1:N78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1299,168 +1317,198 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>60</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>61</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>62</v>
-      </c>
-      <c r="B50">
-        <v>27.2</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>63</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>64</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>65</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>66</v>
+        <v>60</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>68</v>
+        <v>62</v>
+      </c>
+      <c r="B56">
+        <v>27.2</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>69</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>70</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>73</v>
-      </c>
-      <c r="B61">
-        <v>2</v>
+        <v>67</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>74</v>
-      </c>
-      <c r="B62">
-        <v>1</v>
+        <v>68</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>75</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
+        <v>69</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>76</v>
-      </c>
-      <c r="B64">
-        <v>2</v>
+        <v>70</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>77</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>78</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>79</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>89</v>
+        <v>73</v>
+      </c>
+      <c r="B67">
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>80</v>
+        <v>74</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B69">
-        <v>1649</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>82</v>
+        <v>76</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>105</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B78" t="s">
         <v>106</v>
       </c>
     </row>

--- a/data/gravel/Breezer Thunder 2025.xlsx
+++ b/data/gravel/Breezer Thunder 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB329038-DE67-274E-A348-D4D42A1CB3FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B964CAC5-AAC3-764E-8840-026AF1C80869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -338,9 +338,6 @@
     <t>L (19)</t>
   </si>
   <si>
-    <t xml:space="preserve">XL </t>
-  </si>
-  <si>
     <t>flat bar</t>
   </si>
   <si>
@@ -372,6 +369,9 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>XL (21)</t>
   </si>
 </sst>
 </file>
@@ -759,7 +759,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -767,7 +767,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -787,7 +787,7 @@
         <v>100</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -1234,7 +1234,7 @@
         <v>86</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
@@ -1317,32 +1317,32 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
@@ -1506,10 +1506,10 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>104</v>
+      </c>
+      <c r="B78" t="s">
         <v>105</v>
-      </c>
-      <c r="B78" t="s">
-        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Breezer Thunder 2025.xlsx
+++ b/data/gravel/Breezer Thunder 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B964CAC5-AAC3-764E-8840-026AF1C80869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0BD51B-FFE4-9949-8FB1-10F2E72CBE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -341,9 +341,6 @@
     <t>flat bar</t>
   </si>
   <si>
-    <t>a8:f31</t>
-  </si>
-  <si>
     <t>https://www.breezerbikes.com/cdn/shop/files/2021_BREEZER_THUNDER_GRAY_BURNTORANGE.jpg?v=1740772941&amp;width=5000</t>
   </si>
   <si>
@@ -372,6 +369,15 @@
   </si>
   <si>
     <t>XL (21)</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>a8:f33</t>
   </si>
 </sst>
 </file>
@@ -711,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N78"/>
+  <dimension ref="A1:N80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -759,7 +765,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -767,7 +773,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -787,7 +793,7 @@
         <v>100</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -1141,338 +1147,356 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>36</v>
+      <c r="A27" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>39</v>
+      <c r="A28" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="C28">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29">
-        <v>2.8</v>
-      </c>
-      <c r="D29">
-        <v>2.8</v>
-      </c>
-      <c r="E29">
-        <v>2.8</v>
-      </c>
-      <c r="F29">
-        <v>2.8</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C30">
-        <v>160</v>
+        <v>2.5</v>
       </c>
       <c r="D30">
-        <v>167.5</v>
+        <v>2.5</v>
       </c>
       <c r="E30">
-        <v>175</v>
+        <v>2.5</v>
       </c>
       <c r="F30">
-        <v>180.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31">
+        <v>2.8</v>
+      </c>
+      <c r="D31">
+        <v>2.8</v>
+      </c>
+      <c r="E31">
+        <v>2.8</v>
+      </c>
+      <c r="F31">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32">
+        <v>160</v>
+      </c>
+      <c r="D32">
+        <v>167.5</v>
+      </c>
+      <c r="E32">
+        <v>175</v>
+      </c>
+      <c r="F32">
+        <v>180.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>45</v>
       </c>
-      <c r="C31">
+      <c r="C33">
         <v>170</v>
       </c>
-      <c r="D31">
+      <c r="D33">
         <v>178</v>
       </c>
-      <c r="E31">
+      <c r="E33">
         <v>183</v>
       </c>
-      <c r="F31">
+      <c r="F33">
         <v>188</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>46</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B35" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>84</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B36" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>86</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>87</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B38" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>48</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B39" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>52</v>
       </c>
-      <c r="B40">
+      <c r="B42">
         <v>2.8</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>54</v>
       </c>
-      <c r="B42">
+      <c r="B44">
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>58</v>
       </c>
-      <c r="B46">
+      <c r="B48">
         <v>148</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B47">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>107</v>
+        <v>59</v>
+      </c>
+      <c r="B49">
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>60</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>62</v>
-      </c>
-      <c r="B56">
-        <v>27.2</v>
+        <v>60</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>64</v>
+        <v>62</v>
+      </c>
+      <c r="B58">
+        <v>27.2</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>69</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>70</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>71</v>
+        <v>69</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>72</v>
+        <v>70</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>73</v>
-      </c>
-      <c r="B67">
-        <v>2</v>
+        <v>71</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>74</v>
-      </c>
-      <c r="B68">
-        <v>1</v>
+        <v>72</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B69">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>77</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>89</v>
+        <v>75</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>78</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>89</v>
+        <v>76</v>
+      </c>
+      <c r="B72">
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>89</v>
@@ -1480,36 +1504,52 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>80</v>
+        <v>78</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>81</v>
-      </c>
-      <c r="B75">
-        <v>1649</v>
+        <v>79</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>83</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>90</v>
+        <v>81</v>
+      </c>
+      <c r="B77">
+        <v>1649</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>83</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>103</v>
+      </c>
+      <c r="B80" t="s">
         <v>104</v>
-      </c>
-      <c r="B78" t="s">
-        <v>105</v>
       </c>
     </row>
   </sheetData>
